--- a/runs/experiments.xlsx
+++ b/runs/experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/202111181_alu_comillas_edu/Documents/ICAI/Master/RLprof/Practicas/Walker2d_ActorCritic/runs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="438" documentId="11_2B59D2BFD380541E65C3DAF050F0087278A3E60A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BB5200D-EC6E-45CF-B6AA-41DDCA7E8349}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="11_2B59D2BFD380541E65C3DAF050F0087278A3E60A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12510BDC-4021-449F-9D9F-AA61C95BF0C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,6 +210,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -269,7 +272,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -282,6 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,6 +300,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,6 +599,7 @@
     <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
@@ -699,7 +707,7 @@
       <c r="J2" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="M2" s="4">
@@ -717,22 +725,22 @@
       <c r="Q2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="8" t="s">
+      <c r="R2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X2" s="4" t="s">
@@ -773,7 +781,7 @@
       <c r="K3" s="4">
         <v>100.2706807625763</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <v>1E-4</v>
       </c>
       <c r="M3" s="4">
@@ -791,22 +799,22 @@
       <c r="Q3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="8" t="s">
+      <c r="R3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X3" s="4" t="s">
@@ -844,23 +852,22 @@
       <c r="J4" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="R4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="8" t="s">
+      <c r="R4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X4" s="4" t="s">
@@ -901,23 +908,22 @@
       <c r="K5" s="4">
         <v>396.9435169272258</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="R5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W5" s="8" t="s">
+      <c r="R5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X5" s="4" t="s">
@@ -958,23 +964,22 @@
       <c r="K6" s="4">
         <v>2378.7574073014189</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="R6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W6" s="8" t="s">
+      <c r="R6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W6" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X6" s="4" t="s">
@@ -1015,7 +1020,7 @@
       <c r="K7" s="4">
         <v>2059.977799641083</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="M7" s="4">
@@ -1033,22 +1038,22 @@
       <c r="Q7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W7" s="8" t="s">
+      <c r="R7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W7" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X7" s="4" t="s">
@@ -1089,7 +1094,7 @@
       <c r="K8" s="4">
         <v>813.46605732631315</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="4">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="M8" s="4">
@@ -1107,22 +1112,22 @@
       <c r="Q8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W8" s="8" t="s">
+      <c r="R8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W8" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X8" s="4" t="s">
@@ -1163,7 +1168,7 @@
       <c r="K9" s="4">
         <v>991.71225778804512</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="4">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="M9" s="4">
@@ -1181,22 +1186,22 @@
       <c r="Q9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W9" s="8" t="s">
+      <c r="R9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W9" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X9" s="4">
@@ -1237,7 +1242,7 @@
       <c r="K10" s="4">
         <v>1519.04582171637</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="M10" s="4">
@@ -1255,22 +1260,22 @@
       <c r="Q10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="R10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W10" s="8" t="s">
+      <c r="R10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="X10" s="4" t="s">
@@ -1311,7 +1316,7 @@
       <c r="L11" s="3">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N11" s="3">
@@ -1385,7 +1390,7 @@
       <c r="L12" s="3">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N12" s="3">
@@ -1456,7 +1461,7 @@
       <c r="L13" s="3">
         <v>1E-4</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N13" s="3">
@@ -1527,7 +1532,7 @@
       <c r="L14" s="3">
         <v>1E-4</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N14" s="3">
@@ -1601,7 +1606,7 @@
       <c r="L15" s="3">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N15" s="3">
@@ -1672,7 +1677,7 @@
       <c r="L16" s="3">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="N16" s="3">
@@ -1761,22 +1766,22 @@
       <c r="Q17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="V17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="W17" s="9" t="s">
+      <c r="R17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="W17" s="8" t="s">
         <v>41</v>
       </c>
       <c r="X17" s="2" t="s">
@@ -1835,22 +1840,22 @@
       <c r="Q18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="V18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="W18" s="9" t="s">
+      <c r="R18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="W18" s="8" t="s">
         <v>41</v>
       </c>
       <c r="X18" s="2" t="s">
@@ -1891,7 +1896,7 @@
       <c r="L19" s="1">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N19" s="1">
@@ -1962,7 +1967,7 @@
       <c r="L20" s="1">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N20" s="1">
@@ -2027,7 +2032,7 @@
       <c r="L21" s="1">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N21" s="1">
@@ -2049,7 +2054,7 @@
         <v>52</v>
       </c>
       <c r="V21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>51</v>
@@ -2092,7 +2097,7 @@
       <c r="L22" s="1">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N22" s="1">
@@ -2163,10 +2168,10 @@
       <c r="K23" s="1">
         <v>1697.8600234427649</v>
       </c>
-      <c r="L23" s="1">
-        <v>2E-3</v>
-      </c>
-      <c r="M23" s="6" t="s">
+      <c r="L23" s="9">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N23" s="1">
@@ -2205,6 +2210,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
